--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roshani Kumari\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="889" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D410FD0-D704-4322-99B7-62A5713E3274}"/>
+  <xr:revisionPtr revIDLastSave="908" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21251ADD-D9EB-4E52-B9F1-DE36C1BF3D6E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>Today's record: no classes, full weekend time invested in code optimization and study.</t>
+  </si>
+  <si>
+    <t>Sunday routine: Focused more on coding with 5 hours of dedicated practice.</t>
   </si>
 </sst>
 </file>
@@ -662,6 +665,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3276,27 +3283,51 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+    <row r="52" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B52" s="14">
+        <v>360</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>180</v>
+      </c>
+      <c r="E52" s="14">
+        <v>300</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>30</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="908" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21251ADD-D9EB-4E52-B9F1-DE36C1BF3D6E}"/>
+  <xr:revisionPtr revIDLastSave="923" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA45E955-0F80-46EC-842D-6516F4616A1E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Sunday routine: Focused more on coding with 5 hours of dedicated practice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A well-Structured day. Successfully managed to complete 5 classes while hitting the 4 hour daily coding milestone.solid learning progress. </t>
   </si>
 </sst>
 </file>
@@ -3329,27 +3332,51 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+    <row r="53" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B53" s="14">
+        <v>360</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>120</v>
+      </c>
+      <c r="E53" s="14">
+        <v>240</v>
+      </c>
+      <c r="F53" s="14">
+        <v>300</v>
+      </c>
+      <c r="G53" s="14">
+        <v>5</v>
+      </c>
+      <c r="H53" s="14">
+        <v>20</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="923" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA45E955-0F80-46EC-842D-6516F4616A1E}"/>
+  <xr:revisionPtr revIDLastSave="935" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C51A2F5-3C67-47D4-93FC-E8948019E812}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t xml:space="preserve">A well-Structured day. Successfully managed to complete 5 classes while hitting the 4 hour daily coding milestone.solid learning progress. </t>
+  </si>
+  <si>
+    <t>Routine 5 classes completed; standard attention given to coding tasks and self-study.</t>
   </si>
 </sst>
 </file>
@@ -3378,27 +3381,51 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+    <row r="54" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B54" s="14">
+        <v>360</v>
+      </c>
+      <c r="C54" s="14">
+        <v>40</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>240</v>
+      </c>
+      <c r="F54" s="14">
+        <v>300</v>
+      </c>
+      <c r="G54" s="14">
+        <v>5</v>
+      </c>
+      <c r="H54" s="14">
+        <v>20</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="935" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C51A2F5-3C67-47D4-93FC-E8948019E812}"/>
+  <xr:revisionPtr revIDLastSave="949" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF469C04-DA49-4025-98AE-958B0A0A6DBC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>Routine 5 classes completed; standard attention given to coding tasks and self-study.</t>
+  </si>
+  <si>
+    <t>Maintained peak energy levels today. Successfully attended 4 classes and logged 6 hours of core skill building.</t>
   </si>
 </sst>
 </file>
@@ -3427,27 +3430,51 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A55" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B55" s="14">
+        <v>360</v>
+      </c>
+      <c r="C55" s="14">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14">
+        <v>120</v>
+      </c>
+      <c r="E55" s="14">
+        <v>240</v>
+      </c>
+      <c r="F55" s="14">
+        <v>240</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="14">
+        <v>25</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="949" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF469C04-DA49-4025-98AE-958B0A0A6DBC}"/>
+  <xr:revisionPtr revIDLastSave="962" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEBED84-ECE1-45CC-8939-AE5012B79B86}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3476,27 +3476,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+    <row r="56" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B56" s="14">
+        <v>360</v>
+      </c>
+      <c r="C56" s="14">
+        <v>45</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>240</v>
+      </c>
+      <c r="F56" s="14">
+        <v>360</v>
+      </c>
+      <c r="G56" s="14">
+        <v>6</v>
+      </c>
+      <c r="H56" s="14">
+        <v>30</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>285</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="962" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEBED84-ECE1-45CC-8939-AE5012B79B86}"/>
+  <xr:revisionPtr revIDLastSave="1237" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CCDC29-2B83-48E1-8966-4949AB6B76EC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,9 +301,6 @@
     <t>Attended 6 classes; managed evening hours for basic coding and engineering study.</t>
   </si>
   <si>
-    <t>7 classes attended. Pushed through to complete late-night coding and quick study.</t>
-  </si>
-  <si>
     <t>Class-free day; completely invested in complex script building and library studies.</t>
   </si>
   <si>
@@ -380,6 +377,9 @@
   </si>
   <si>
     <t>Maintained peak energy levels today. Successfully attended 4 classes and logged 6 hours of core skill building.</t>
+  </si>
+  <si>
+    <t>7 classes attended. Pushed through to complete coding and quick study.</t>
   </si>
 </sst>
 </file>
@@ -1227,16 +1227,16 @@
         <v>46240</v>
       </c>
       <c r="B7" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C7" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E7" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F7" s="14">
         <v>360</v>
@@ -1245,15 +1245,15 @@
         <v>6</v>
       </c>
       <c r="H7" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1135</v>
+        <v>960</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>305</v>
+        <v>480</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
@@ -1273,16 +1273,16 @@
         <v>46241</v>
       </c>
       <c r="B8" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D8" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E8" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F8" s="14">
         <v>420</v>
@@ -1291,15 +1291,15 @@
         <v>7</v>
       </c>
       <c r="H8" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>1205</v>
+        <v>1010</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>235</v>
+        <v>430</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>61</v>
@@ -1319,16 +1319,16 @@
         <v>46242</v>
       </c>
       <c r="B9" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C9" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D9" s="14">
         <v>180</v>
       </c>
       <c r="E9" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F9" s="14">
         <v>0</v>
@@ -1337,15 +1337,15 @@
         <v>0</v>
       </c>
       <c r="H9" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>62</v>
@@ -1365,7 +1365,7 @@
         <v>46243</v>
       </c>
       <c r="B10" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C10" s="14">
         <v>30</v>
@@ -1374,7 +1374,7 @@
         <v>180</v>
       </c>
       <c r="E10" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F10" s="14">
         <v>0</v>
@@ -1383,15 +1383,15 @@
         <v>0</v>
       </c>
       <c r="H10" s="14">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>870</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>63</v>
@@ -1411,16 +1411,16 @@
         <v>46244</v>
       </c>
       <c r="B11" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C11" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E11" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F11" s="14">
         <v>300</v>
@@ -1429,15 +1429,15 @@
         <v>5</v>
       </c>
       <c r="H11" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1085</v>
+        <v>960</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>355</v>
+        <v>480</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>64</v>
@@ -1457,16 +1457,16 @@
         <v>46245</v>
       </c>
       <c r="B12" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
         <v>30</v>
       </c>
       <c r="D12" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E12" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F12" s="14">
         <v>300</v>
@@ -1475,15 +1475,15 @@
         <v>5</v>
       </c>
       <c r="H12" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1075</v>
+        <v>960</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>365</v>
+        <v>480</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1503,16 +1503,16 @@
         <v>46246</v>
       </c>
       <c r="B13" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D13" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E13" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F13" s="14">
         <v>240</v>
@@ -1525,11 +1525,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1025</v>
+        <v>880</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>415</v>
+        <v>560</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>65</v>
@@ -1549,16 +1549,16 @@
         <v>46247</v>
       </c>
       <c r="B14" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C14" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E14" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F14" s="14">
         <v>360</v>
@@ -1567,15 +1567,15 @@
         <v>6</v>
       </c>
       <c r="H14" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1135</v>
+        <v>960</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>305</v>
+        <v>480</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>57</v>
@@ -1595,16 +1595,16 @@
         <v>46248</v>
       </c>
       <c r="B15" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C15" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E15" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
         <v>420</v>
@@ -1613,15 +1613,15 @@
         <v>7</v>
       </c>
       <c r="H15" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1195</v>
+        <v>1010</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>245</v>
+        <v>430</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>61</v>
@@ -1641,16 +1641,16 @@
         <v>46249</v>
       </c>
       <c r="B16" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C16" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
         <v>180</v>
       </c>
       <c r="E16" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
         <v>0</v>
@@ -1659,15 +1659,15 @@
         <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>62</v>
@@ -1687,16 +1687,16 @@
         <v>46250</v>
       </c>
       <c r="B17" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C17" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
         <v>180</v>
       </c>
       <c r="E17" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F17" s="14">
         <v>0</v>
@@ -1705,15 +1705,15 @@
         <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>63</v>
@@ -1733,16 +1733,16 @@
         <v>46251</v>
       </c>
       <c r="B18" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C18" s="14">
         <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E18" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F18" s="14">
         <v>300</v>
@@ -1751,15 +1751,15 @@
         <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1065</v>
+        <v>960</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>64</v>
@@ -1779,16 +1779,16 @@
         <v>46252</v>
       </c>
       <c r="B19" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E19" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F19" s="14">
         <v>300</v>
@@ -1797,15 +1797,15 @@
         <v>5</v>
       </c>
       <c r="H19" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1085</v>
+        <v>960</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>355</v>
+        <v>480</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1825,16 +1825,16 @@
         <v>46253</v>
       </c>
       <c r="B20" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E20" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F20" s="14">
         <v>240</v>
@@ -1843,15 +1843,15 @@
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1025</v>
+        <v>880</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>415</v>
+        <v>560</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>65</v>
@@ -1871,16 +1871,16 @@
         <v>46254</v>
       </c>
       <c r="B21" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C21" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D21" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E21" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F21" s="14">
         <v>360</v>
@@ -1893,11 +1893,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1145</v>
+        <v>960</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>295</v>
+        <v>480</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
@@ -1917,16 +1917,16 @@
         <v>46255</v>
       </c>
       <c r="B22" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C22" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E22" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F22" s="14">
         <v>420</v>
@@ -1935,15 +1935,15 @@
         <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1185</v>
+        <v>1010</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>430</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>61</v>
@@ -1963,16 +1963,16 @@
         <v>46256</v>
       </c>
       <c r="B23" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C23" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D23" s="14">
         <v>180</v>
       </c>
       <c r="E23" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F23" s="14">
         <v>0</v>
@@ -1981,15 +1981,15 @@
         <v>0</v>
       </c>
       <c r="H23" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>62</v>
@@ -2009,16 +2009,16 @@
         <v>46257</v>
       </c>
       <c r="B24" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
         <v>180</v>
       </c>
       <c r="E24" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F24" s="14">
         <v>0</v>
@@ -2027,15 +2027,15 @@
         <v>0</v>
       </c>
       <c r="H24" s="14">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>63</v>
@@ -2055,16 +2055,16 @@
         <v>46258</v>
       </c>
       <c r="B25" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C25" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E25" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F25" s="14">
         <v>5</v>
@@ -2077,11 +2077,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>795</v>
+        <v>665</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>645</v>
+        <v>775</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>64</v>
@@ -2101,16 +2101,16 @@
         <v>46259</v>
       </c>
       <c r="B26" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C26" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E26" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F26" s="14">
         <v>5</v>
@@ -2119,15 +2119,15 @@
         <v>5</v>
       </c>
       <c r="H26" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>775</v>
+        <v>665</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>665</v>
+        <v>775</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -2147,16 +2147,16 @@
         <v>46260</v>
       </c>
       <c r="B27" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C27" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D27" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E27" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -2165,15 +2165,15 @@
         <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>789</v>
+        <v>644</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>651</v>
+        <v>796</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>65</v>
@@ -2193,16 +2193,16 @@
         <v>46261</v>
       </c>
       <c r="B28" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C28" s="14">
         <v>30</v>
       </c>
       <c r="D28" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E28" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
@@ -2211,15 +2211,15 @@
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>781</v>
+        <v>606</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>659</v>
+        <v>834</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>57</v>
@@ -2239,16 +2239,16 @@
         <v>46262</v>
       </c>
       <c r="B29" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C29" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E29" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F29" s="14">
         <v>7</v>
@@ -2261,11 +2261,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>797</v>
+        <v>597</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>643</v>
+        <v>843</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>61</v>
@@ -2277,7 +2277,7 @@
         <v>59</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2285,16 +2285,16 @@
         <v>46263</v>
       </c>
       <c r="B30" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C30" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14">
         <v>180</v>
       </c>
       <c r="E30" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14">
         <v>0</v>
@@ -2303,15 +2303,15 @@
         <v>0</v>
       </c>
       <c r="H30" s="14">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>62</v>
@@ -2323,7 +2323,7 @@
         <v>66</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2331,16 +2331,16 @@
         <v>46264</v>
       </c>
       <c r="B31" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C31" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D31" s="14">
         <v>180</v>
       </c>
       <c r="E31" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F31" s="14">
         <v>0</v>
@@ -2349,15 +2349,15 @@
         <v>0</v>
       </c>
       <c r="H31" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>63</v>
@@ -2369,7 +2369,7 @@
         <v>66</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2377,16 +2377,16 @@
         <v>46265</v>
       </c>
       <c r="B32" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C32" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D32" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E32" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F32" s="14">
         <v>300</v>
@@ -2395,15 +2395,15 @@
         <v>5</v>
       </c>
       <c r="H32" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>64</v>
@@ -2415,7 +2415,7 @@
         <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2423,16 +2423,16 @@
         <v>46266</v>
       </c>
       <c r="B33" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C33" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D33" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E33" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F33" s="14">
         <v>300</v>
@@ -2445,11 +2445,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>960</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>49</v>
@@ -2461,7 +2461,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2469,16 +2469,16 @@
         <v>46267</v>
       </c>
       <c r="B34" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C34" s="14">
         <v>30</v>
       </c>
       <c r="D34" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E34" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F34" s="14">
         <v>240</v>
@@ -2487,15 +2487,15 @@
         <v>4</v>
       </c>
       <c r="H34" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1005</v>
+        <v>880</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>435</v>
+        <v>560</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>65</v>
@@ -2507,7 +2507,7 @@
         <v>66</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2515,16 +2515,16 @@
         <v>46268</v>
       </c>
       <c r="B35" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C35" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D35" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E35" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F35" s="14">
         <v>360</v>
@@ -2533,15 +2533,15 @@
         <v>6</v>
       </c>
       <c r="H35" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1145</v>
+        <v>960</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>295</v>
+        <v>480</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>57</v>
@@ -2553,7 +2553,7 @@
         <v>59</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2561,16 +2561,16 @@
         <v>46269</v>
       </c>
       <c r="B36" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C36" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D36" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E36" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F36" s="14">
         <v>420</v>
@@ -2579,15 +2579,15 @@
         <v>7</v>
       </c>
       <c r="H36" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1010</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>61</v>
@@ -2599,7 +2599,7 @@
         <v>59</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2607,7 +2607,7 @@
         <v>46270</v>
       </c>
       <c r="B37" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C37" s="14">
         <v>30</v>
@@ -2616,7 +2616,7 @@
         <v>180</v>
       </c>
       <c r="E37" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F37" s="14">
         <v>0</v>
@@ -2625,15 +2625,15 @@
         <v>0</v>
       </c>
       <c r="H37" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>62</v>
@@ -2645,7 +2645,7 @@
         <v>66</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -2653,16 +2653,16 @@
         <v>46271</v>
       </c>
       <c r="B38" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C38" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14">
         <v>180</v>
       </c>
       <c r="E38" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F38" s="14">
         <v>0</v>
@@ -2671,15 +2671,15 @@
         <v>0</v>
       </c>
       <c r="H38" s="14">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>63</v>
@@ -2691,7 +2691,7 @@
         <v>66</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2699,16 +2699,16 @@
         <v>46272</v>
       </c>
       <c r="B39" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C39" s="14">
         <v>30</v>
       </c>
       <c r="D39" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E39" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F39" s="14">
         <v>300</v>
@@ -2717,15 +2717,15 @@
         <v>5</v>
       </c>
       <c r="H39" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>960</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>64</v>
@@ -2737,7 +2737,7 @@
         <v>51</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2745,16 +2745,16 @@
         <v>46273</v>
       </c>
       <c r="B40" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C40" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D40" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E40" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F40" s="14">
         <v>300</v>
@@ -2763,15 +2763,15 @@
         <v>5</v>
       </c>
       <c r="H40" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>49</v>
@@ -2783,7 +2783,7 @@
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2791,16 +2791,16 @@
         <v>46274</v>
       </c>
       <c r="B41" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
         <v>30</v>
       </c>
       <c r="D41" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E41" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F41" s="14">
         <v>240</v>
@@ -2813,11 +2813,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>880</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>560</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>65</v>
@@ -2829,7 +2829,7 @@
         <v>66</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2837,16 +2837,16 @@
         <v>46275</v>
       </c>
       <c r="B42" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C42" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D42" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E42" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F42" s="14">
         <v>360</v>
@@ -2855,15 +2855,15 @@
         <v>6</v>
       </c>
       <c r="H42" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>960</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>57</v>
@@ -2875,7 +2875,7 @@
         <v>59</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2883,16 +2883,16 @@
         <v>46276</v>
       </c>
       <c r="B43" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C43" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D43" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E43" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F43" s="14">
         <v>420</v>
@@ -2901,15 +2901,15 @@
         <v>7</v>
       </c>
       <c r="H43" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1010</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>61</v>
@@ -2921,7 +2921,7 @@
         <v>59</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -2929,7 +2929,7 @@
         <v>46277</v>
       </c>
       <c r="B44" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C44" s="14">
         <v>30</v>
@@ -2938,7 +2938,7 @@
         <v>180</v>
       </c>
       <c r="E44" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F44" s="14">
         <v>0</v>
@@ -2947,15 +2947,15 @@
         <v>0</v>
       </c>
       <c r="H44" s="14">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>62</v>
@@ -2967,7 +2967,7 @@
         <v>66</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2975,16 +2975,16 @@
         <v>46278</v>
       </c>
       <c r="B45" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C45" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D45" s="14">
         <v>180</v>
       </c>
       <c r="E45" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F45" s="14">
         <v>0</v>
@@ -2993,15 +2993,15 @@
         <v>0</v>
       </c>
       <c r="H45" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>63</v>
@@ -3013,7 +3013,7 @@
         <v>66</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3021,16 +3021,16 @@
         <v>46279</v>
       </c>
       <c r="B46" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C46" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D46" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E46" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F46" s="14">
         <v>300</v>
@@ -3039,15 +3039,15 @@
         <v>5</v>
       </c>
       <c r="H46" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>960</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>64</v>
@@ -3059,7 +3059,7 @@
         <v>51</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3067,16 +3067,16 @@
         <v>46280</v>
       </c>
       <c r="B47" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C47" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D47" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E47" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F47" s="14">
         <v>300</v>
@@ -3085,15 +3085,15 @@
         <v>5</v>
       </c>
       <c r="H47" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>49</v>
@@ -3105,7 +3105,7 @@
         <v>51</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3113,16 +3113,16 @@
         <v>46281</v>
       </c>
       <c r="B48" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C48" s="14">
         <v>30</v>
       </c>
       <c r="D48" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E48" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F48" s="14">
         <v>240</v>
@@ -3131,15 +3131,15 @@
         <v>4</v>
       </c>
       <c r="H48" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>1015</v>
+        <v>880</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>425</v>
+        <v>560</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>65</v>
@@ -3151,7 +3151,7 @@
         <v>66</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3159,16 +3159,16 @@
         <v>46282</v>
       </c>
       <c r="B49" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C49" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D49" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E49" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F49" s="14">
         <v>360</v>
@@ -3181,11 +3181,11 @@
       </c>
       <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v>1155</v>
+        <v>960</v>
       </c>
       <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>57</v>
@@ -3197,7 +3197,7 @@
         <v>59</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3205,16 +3205,16 @@
         <v>46283</v>
       </c>
       <c r="B50" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C50" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D50" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E50" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F50" s="14">
         <v>420</v>
@@ -3223,15 +3223,15 @@
         <v>7</v>
       </c>
       <c r="H50" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1010</v>
       </c>
       <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>61</v>
@@ -3243,7 +3243,7 @@
         <v>59</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3251,16 +3251,16 @@
         <v>46284</v>
       </c>
       <c r="B51" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C51" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D51" s="14">
         <v>180</v>
       </c>
       <c r="E51" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F51" s="14">
         <v>0</v>
@@ -3269,15 +3269,15 @@
         <v>0</v>
       </c>
       <c r="H51" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>62</v>
@@ -3289,7 +3289,7 @@
         <v>66</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3297,7 +3297,7 @@
         <v>46285</v>
       </c>
       <c r="B52" s="14">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C52" s="14">
         <v>30</v>
@@ -3306,7 +3306,7 @@
         <v>180</v>
       </c>
       <c r="E52" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F52" s="14">
         <v>0</v>
@@ -3315,15 +3315,15 @@
         <v>0</v>
       </c>
       <c r="H52" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>64</v>
@@ -3335,7 +3335,7 @@
         <v>66</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="87" x14ac:dyDescent="0.35">
@@ -3343,16 +3343,16 @@
         <v>46286</v>
       </c>
       <c r="B53" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
       </c>
       <c r="D53" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E53" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F53" s="14">
         <v>300</v>
@@ -3361,15 +3361,15 @@
         <v>5</v>
       </c>
       <c r="H53" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>960</v>
       </c>
       <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>49</v>
@@ -3381,7 +3381,7 @@
         <v>51</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3389,16 +3389,16 @@
         <v>46287</v>
       </c>
       <c r="B54" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C54" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D54" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E54" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="F54" s="14">
         <v>300</v>
@@ -3407,15 +3407,15 @@
         <v>5</v>
       </c>
       <c r="H54" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="K54" s="16" t="s">
         <v>49</v>
@@ -3427,7 +3427,7 @@
         <v>51</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -3435,16 +3435,16 @@
         <v>46288</v>
       </c>
       <c r="B55" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C55" s="14">
         <v>30</v>
       </c>
       <c r="D55" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E55" s="14">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F55" s="14">
         <v>240</v>
@@ -3453,15 +3453,15 @@
         <v>4</v>
       </c>
       <c r="H55" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v>1015</v>
+        <v>880</v>
       </c>
       <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v>425</v>
+        <v>560</v>
       </c>
       <c r="K55" s="16" t="s">
         <v>65</v>
@@ -3473,7 +3473,7 @@
         <v>66</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3481,16 +3481,16 @@
         <v>46289</v>
       </c>
       <c r="B56" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C56" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D56" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E56" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F56" s="14">
         <v>360</v>
@@ -3503,11 +3503,11 @@
       </c>
       <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v>1155</v>
+        <v>960</v>
       </c>
       <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>57</v>
@@ -3519,30 +3519,54 @@
         <v>59</v>
       </c>
       <c r="N56" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>20</v>
+      </c>
+      <c r="D57" s="14">
+        <v>60</v>
+      </c>
+      <c r="E57" s="14">
+        <v>60</v>
+      </c>
+      <c r="F57" s="14">
+        <v>420</v>
+      </c>
+      <c r="G57" s="14">
+        <v>7</v>
+      </c>
+      <c r="H57" s="14">
+        <v>30</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N57" s="17" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1237" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CCDC29-2B83-48E1-8966-4949AB6B76EC}"/>
+  <xr:revisionPtr revIDLastSave="1250" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B17D96-9A86-4A4E-9418-E8E2B15EF97B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>7 classes attended. Pushed through to complete coding and quick study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No classes today, so had the perfect chance to focus entirely on self-study and coding. </t>
   </si>
 </sst>
 </file>
@@ -3568,27 +3571,51 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+    <row r="58" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B58" s="14">
+        <v>480</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>180</v>
+      </c>
+      <c r="E58" s="14">
+        <v>120</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>60</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1250" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B17D96-9A86-4A4E-9418-E8E2B15EF97B}"/>
+  <xr:revisionPtr revIDLastSave="1264" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C42D191F-797F-4F36-8E60-C33E736B6F97}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t xml:space="preserve">No classes today, so had the perfect chance to focus entirely on self-study and coding. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since there were no classes scheduled today, it provided a perfect opportunity to fully focus on self-study and coding. </t>
   </si>
 </sst>
 </file>
@@ -3617,27 +3623,51 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+    <row r="59" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>30</v>
+      </c>
+      <c r="D59" s="14">
+        <v>180</v>
+      </c>
+      <c r="E59" s="14">
+        <v>120</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>60</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1264" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C42D191F-797F-4F36-8E60-C33E736B6F97}"/>
+  <xr:revisionPtr revIDLastSave="1307" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C85C7ED3-7B7A-4970-A505-C784B4E5AFDC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,21 @@
   </si>
   <si>
     <t xml:space="preserve">Since there were no classes scheduled today, it provided a perfect opportunity to fully focus on self-study and coding. </t>
+  </si>
+  <si>
+    <t>No classes due to college protest, focused entirely on self study and coding sessions.</t>
+  </si>
+  <si>
+    <t>Anxious</t>
+  </si>
+  <si>
+    <t>Dissatisfied</t>
+  </si>
+  <si>
+    <t>Traveled today due to the ongoing college protest.All academic activities and logs are zero for day.</t>
+  </si>
+  <si>
+    <t>Traveled due to college protest and got tired. Since mid-terms are approaching. Focused more on increasing my study time.</t>
   </si>
 </sst>
 </file>
@@ -3669,37 +3684,77 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+    <row r="60" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>20</v>
+      </c>
+      <c r="D60" s="14">
+        <v>100</v>
+      </c>
+      <c r="E60" s="14">
+        <v>90</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>60</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
+        <v>750</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B61" s="14">
+        <v>0</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>0</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>0</v>
+      </c>
       <c r="I61" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3708,32 +3763,64 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="K61" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A62" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B62" s="14">
+        <v>480</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>240</v>
+      </c>
+      <c r="E62" s="14">
+        <v>90</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>30</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1307" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C85C7ED3-7B7A-4970-A505-C784B4E5AFDC}"/>
+  <xr:revisionPtr revIDLastSave="1323" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AC5FBE2-979D-4E3F-AB63-D6B656B65884}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>Traveled due to college protest and got tired. Since mid-terms are approaching. Focused more on increasing my study time.</t>
+  </si>
+  <si>
+    <t>Mid-terms are approaching, so I have increased my study and coding time.</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1677,7 @@
         <v>180</v>
       </c>
       <c r="E16" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
         <v>0</v>
@@ -1687,11 +1690,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>62</v>
@@ -1858,7 +1861,7 @@
         <v>90</v>
       </c>
       <c r="E20" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F20" s="14">
         <v>240</v>
@@ -1871,11 +1874,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>65</v>
@@ -3143,7 +3146,7 @@
         <v>30</v>
       </c>
       <c r="D48" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E48" s="14">
         <v>70</v>
@@ -3159,11 +3162,11 @@
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>65</v>
@@ -3822,27 +3825,51 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+    <row r="63" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B63" s="14">
+        <v>480</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>360</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>30</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1323" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AC5FBE2-979D-4E3F-AB63-D6B656B65884}"/>
+  <xr:revisionPtr revIDLastSave="1336" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D4A9D06-B430-471C-8748-91D77A87749A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>Mid-terms are approaching, so I have increased my study and coding time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excellent balance between learning and coding kept the energy high and mood satisfied. </t>
   </si>
 </sst>
 </file>
@@ -3871,27 +3874,51 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+    <row r="64" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B64" s="14">
+        <v>480</v>
+      </c>
+      <c r="C64" s="14">
+        <v>25</v>
+      </c>
+      <c r="D64" s="14">
+        <v>360</v>
+      </c>
+      <c r="E64" s="14">
+        <v>120</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>30</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1336" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D4A9D06-B430-471C-8748-91D77A87749A}"/>
+  <xr:revisionPtr revIDLastSave="1348" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ADEE4D3-527A-4DDC-AF68-7E65407337DF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t xml:space="preserve">Excellent balance between learning and coding kept the energy high and mood satisfied. </t>
+  </si>
+  <si>
+    <t>Good balance between learning and coding kept the energy high and mood satisfied.</t>
   </si>
 </sst>
 </file>
@@ -3920,27 +3923,51 @@
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+    <row r="65" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B65" s="14">
+        <v>480</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>360</v>
+      </c>
+      <c r="E65" s="14">
+        <v>110</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>30</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1348" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ADEE4D3-527A-4DDC-AF68-7E65407337DF}"/>
+  <xr:revisionPtr revIDLastSave="1507" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF1FECB-A5F7-4E91-92AE-6CA1423CDD2B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -364,15 +364,6 @@
     <t>Managed 7 classes. Successfully achieved set target for code analysis and study.</t>
   </si>
   <si>
-    <t>Today's record: no classes, full weekend time invested in code optimization and study.</t>
-  </si>
-  <si>
-    <t>Sunday routine: Focused more on coding with 5 hours of dedicated practice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A well-Structured day. Successfully managed to complete 5 classes while hitting the 4 hour daily coding milestone.solid learning progress. </t>
-  </si>
-  <si>
     <t>Routine 5 classes completed; standard attention given to coding tasks and self-study.</t>
   </si>
   <si>
@@ -412,7 +403,16 @@
     <t xml:space="preserve">Excellent balance between learning and coding kept the energy high and mood satisfied. </t>
   </si>
   <si>
-    <t>Good balance between learning and coding kept the energy high and mood satisfied.</t>
+    <t>No classes, full weekend time invested in code optimization and study.</t>
+  </si>
+  <si>
+    <t>A wonderful and highly productive day where all goals were beautifully met.</t>
+  </si>
+  <si>
+    <t>No classes today, but the productivity remained unmatched. Kept the energy high and ended the day felling thoroughly satisfied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Good balance between learning and coding kept the energy high and mood satisfied.</t>
   </si>
 </sst>
 </file>
@@ -1266,13 +1266,13 @@
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E7" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F7" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G7" s="14">
         <v>6</v>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E8" s="14">
         <v>60</v>
       </c>
       <c r="F8" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G8" s="14">
         <v>7</v>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>61</v>
@@ -1355,10 +1355,10 @@
         <v>480</v>
       </c>
       <c r="C9" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D9" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E9" s="14">
         <v>120</v>
@@ -1374,11 +1374,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>62</v>
@@ -1401,10 +1401,10 @@
         <v>480</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D10" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E10" s="14">
         <v>120</v>
@@ -1420,11 +1420,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>63</v>
@@ -1450,13 +1450,13 @@
         <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E11" s="14">
         <v>90</v>
       </c>
       <c r="F11" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G11" s="14">
         <v>5</v>
@@ -1466,11 +1466,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>64</v>
@@ -1496,13 +1496,13 @@
         <v>30</v>
       </c>
       <c r="D12" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E12" s="14">
         <v>90</v>
       </c>
       <c r="F12" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G12" s="14">
         <v>5</v>
@@ -1512,11 +1512,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1539,16 +1539,16 @@
         <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D13" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E13" s="14">
         <v>70</v>
       </c>
       <c r="F13" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G13" s="14">
         <v>4</v>
@@ -1558,11 +1558,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>490</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>65</v>
@@ -1588,13 +1588,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E14" s="14">
         <v>60</v>
       </c>
       <c r="F14" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G14" s="14">
         <v>6</v>
@@ -1604,11 +1604,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>57</v>
@@ -1634,13 +1634,13 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
         <v>60</v>
       </c>
       <c r="F15" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>61</v>
@@ -1677,10 +1677,10 @@
         <v>480</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D16" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E16" s="14">
         <v>150</v>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>62</v>
@@ -1723,10 +1723,10 @@
         <v>480</v>
       </c>
       <c r="C17" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D17" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E17" s="14">
         <v>120</v>
@@ -1742,11 +1742,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>63</v>
@@ -1772,13 +1772,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E18" s="14">
         <v>90</v>
       </c>
       <c r="F18" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
@@ -1788,11 +1788,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>64</v>
@@ -1818,13 +1818,13 @@
         <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E19" s="14">
         <v>90</v>
       </c>
       <c r="F19" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G19" s="14">
         <v>5</v>
@@ -1834,11 +1834,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1864,13 +1864,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E20" s="14">
         <v>75</v>
       </c>
       <c r="F20" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
@@ -1880,11 +1880,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>885</v>
+        <v>945</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>65</v>
@@ -1910,13 +1910,13 @@
         <v>30</v>
       </c>
       <c r="D21" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E21" s="14">
         <v>60</v>
       </c>
       <c r="F21" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
         <v>6</v>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
@@ -1956,13 +1956,13 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E22" s="14">
         <v>60</v>
       </c>
       <c r="F22" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G22" s="14">
         <v>7</v>
@@ -1972,11 +1972,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>61</v>
@@ -1999,10 +1999,10 @@
         <v>480</v>
       </c>
       <c r="C23" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E23" s="14">
         <v>120</v>
@@ -2018,11 +2018,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>62</v>
@@ -2045,10 +2045,10 @@
         <v>480</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D24" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E24" s="14">
         <v>120</v>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>63</v>
@@ -2094,13 +2094,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E25" s="14">
         <v>90</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="G25" s="14">
         <v>5</v>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>665</v>
+        <v>1000</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>775</v>
+        <v>440</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>64</v>
@@ -2140,13 +2140,13 @@
         <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E26" s="14">
         <v>90</v>
       </c>
       <c r="F26" s="14">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="G26" s="14">
         <v>5</v>
@@ -2156,11 +2156,11 @@
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>665</v>
+        <v>1000</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>775</v>
+        <v>440</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -2186,13 +2186,13 @@
         <v>30</v>
       </c>
       <c r="D27" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E27" s="14">
         <v>70</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
@@ -2202,11 +2202,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>644</v>
+        <v>940</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>796</v>
+        <v>500</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>65</v>
@@ -2232,13 +2232,13 @@
         <v>30</v>
       </c>
       <c r="D28" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E28" s="14">
         <v>60</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
@@ -2248,11 +2248,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>606</v>
+        <v>990</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>834</v>
+        <v>450</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>57</v>
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="F29" s="14">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="G29" s="14">
         <v>7</v>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>597</v>
+        <v>940</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>843</v>
+        <v>500</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>61</v>
@@ -2310,7 +2310,7 @@
         <v>59</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2321,10 +2321,10 @@
         <v>480</v>
       </c>
       <c r="C30" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D30" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E30" s="14">
         <v>120</v>
@@ -2340,11 +2340,11 @@
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>62</v>
@@ -2367,10 +2367,10 @@
         <v>480</v>
       </c>
       <c r="C31" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D31" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E31" s="14">
         <v>120</v>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>63</v>
@@ -2416,13 +2416,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E32" s="14">
         <v>90</v>
       </c>
       <c r="F32" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G32" s="14">
         <v>5</v>
@@ -2432,11 +2432,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>64</v>
@@ -2462,13 +2462,13 @@
         <v>30</v>
       </c>
       <c r="D33" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E33" s="14">
         <v>90</v>
       </c>
       <c r="F33" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G33" s="14">
         <v>5</v>
@@ -2478,11 +2478,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>49</v>
@@ -2508,13 +2508,13 @@
         <v>30</v>
       </c>
       <c r="D34" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E34" s="14">
         <v>70</v>
       </c>
       <c r="F34" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G34" s="14">
         <v>4</v>
@@ -2524,11 +2524,11 @@
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>940</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>65</v>
@@ -2554,13 +2554,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E35" s="14">
         <v>60</v>
       </c>
       <c r="F35" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G35" s="14">
         <v>6</v>
@@ -2570,11 +2570,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>57</v>
@@ -2600,13 +2600,13 @@
         <v>20</v>
       </c>
       <c r="D36" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E36" s="14">
         <v>60</v>
       </c>
       <c r="F36" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G36" s="14">
         <v>7</v>
@@ -2616,11 +2616,11 @@
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>61</v>
@@ -2643,10 +2643,10 @@
         <v>480</v>
       </c>
       <c r="C37" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D37" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E37" s="14">
         <v>120</v>
@@ -2662,11 +2662,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>62</v>
@@ -2689,10 +2689,10 @@
         <v>480</v>
       </c>
       <c r="C38" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D38" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E38" s="14">
         <v>120</v>
@@ -2708,11 +2708,11 @@
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>63</v>
@@ -2738,13 +2738,13 @@
         <v>30</v>
       </c>
       <c r="D39" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E39" s="14">
         <v>90</v>
       </c>
       <c r="F39" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G39" s="14">
         <v>5</v>
@@ -2754,11 +2754,11 @@
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>64</v>
@@ -2784,13 +2784,13 @@
         <v>30</v>
       </c>
       <c r="D40" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E40" s="14">
         <v>90</v>
       </c>
       <c r="F40" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G40" s="14">
         <v>5</v>
@@ -2800,11 +2800,11 @@
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>49</v>
@@ -2830,13 +2830,13 @@
         <v>30</v>
       </c>
       <c r="D41" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E41" s="14">
         <v>70</v>
       </c>
       <c r="F41" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G41" s="14">
         <v>4</v>
@@ -2846,11 +2846,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>940</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>65</v>
@@ -2876,13 +2876,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E42" s="14">
         <v>60</v>
       </c>
       <c r="F42" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G42" s="14">
         <v>6</v>
@@ -2892,11 +2892,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>57</v>
@@ -2922,13 +2922,13 @@
         <v>20</v>
       </c>
       <c r="D43" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E43" s="14">
         <v>60</v>
       </c>
       <c r="F43" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G43" s="14">
         <v>7</v>
@@ -2938,11 +2938,11 @@
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>61</v>
@@ -2965,10 +2965,10 @@
         <v>480</v>
       </c>
       <c r="C44" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D44" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E44" s="14">
         <v>120</v>
@@ -2984,11 +2984,11 @@
       </c>
       <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>62</v>
@@ -3011,10 +3011,10 @@
         <v>480</v>
       </c>
       <c r="C45" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D45" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E45" s="14">
         <v>120</v>
@@ -3030,11 +3030,11 @@
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>63</v>
@@ -3060,13 +3060,13 @@
         <v>30</v>
       </c>
       <c r="D46" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E46" s="14">
         <v>90</v>
       </c>
       <c r="F46" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G46" s="14">
         <v>5</v>
@@ -3076,11 +3076,11 @@
       </c>
       <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>64</v>
@@ -3106,13 +3106,13 @@
         <v>30</v>
       </c>
       <c r="D47" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E47" s="14">
         <v>90</v>
       </c>
       <c r="F47" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G47" s="14">
         <v>5</v>
@@ -3122,11 +3122,11 @@
       </c>
       <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>49</v>
@@ -3152,13 +3152,13 @@
         <v>30</v>
       </c>
       <c r="D48" s="14">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="E48" s="14">
         <v>70</v>
       </c>
       <c r="F48" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G48" s="14">
         <v>4</v>
@@ -3168,11 +3168,11 @@
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>940</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>65</v>
@@ -3198,13 +3198,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E49" s="14">
         <v>60</v>
       </c>
       <c r="F49" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G49" s="14">
         <v>6</v>
@@ -3214,11 +3214,11 @@
       </c>
       <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>57</v>
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="D50" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E50" s="14">
         <v>60</v>
       </c>
       <c r="F50" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G50" s="14">
         <v>7</v>
@@ -3260,11 +3260,11 @@
       </c>
       <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>61</v>
@@ -3287,10 +3287,10 @@
         <v>480</v>
       </c>
       <c r="C51" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D51" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E51" s="14">
         <v>120</v>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>62</v>
@@ -3322,7 +3322,7 @@
         <v>66</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3333,10 +3333,10 @@
         <v>480</v>
       </c>
       <c r="C52" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D52" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E52" s="14">
         <v>120</v>
@@ -3352,11 +3352,11 @@
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>64</v>
@@ -3368,10 +3368,10 @@
         <v>66</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="13">
         <v>46286</v>
       </c>
@@ -3382,13 +3382,13 @@
         <v>30</v>
       </c>
       <c r="D53" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E53" s="14">
         <v>90</v>
       </c>
       <c r="F53" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G53" s="14">
         <v>5</v>
@@ -3398,11 +3398,11 @@
       </c>
       <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>49</v>
@@ -3414,7 +3414,7 @@
         <v>51</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3428,13 +3428,13 @@
         <v>30</v>
       </c>
       <c r="D54" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E54" s="14">
         <v>90</v>
       </c>
       <c r="F54" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G54" s="14">
         <v>5</v>
@@ -3444,11 +3444,11 @@
       </c>
       <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="K54" s="16" t="s">
         <v>49</v>
@@ -3460,7 +3460,7 @@
         <v>51</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -3474,13 +3474,13 @@
         <v>30</v>
       </c>
       <c r="D55" s="14">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E55" s="14">
         <v>70</v>
       </c>
       <c r="F55" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G55" s="14">
         <v>4</v>
@@ -3490,11 +3490,11 @@
       </c>
       <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>940</v>
       </c>
       <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="K55" s="16" t="s">
         <v>65</v>
@@ -3506,7 +3506,7 @@
         <v>66</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3520,13 +3520,13 @@
         <v>30</v>
       </c>
       <c r="D56" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E56" s="14">
         <v>60</v>
       </c>
       <c r="F56" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G56" s="14">
         <v>6</v>
@@ -3536,11 +3536,11 @@
       </c>
       <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>57</v>
@@ -3566,13 +3566,13 @@
         <v>20</v>
       </c>
       <c r="D57" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E57" s="14">
         <v>60</v>
       </c>
       <c r="F57" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G57" s="14">
         <v>7</v>
@@ -3582,11 +3582,11 @@
       </c>
       <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>61</v>
@@ -3609,10 +3609,10 @@
         <v>480</v>
       </c>
       <c r="C58" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D58" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E58" s="14">
         <v>120</v>
@@ -3628,11 +3628,11 @@
       </c>
       <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K58" s="16" t="s">
         <v>62</v>
@@ -3644,7 +3644,7 @@
         <v>66</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -3655,10 +3655,10 @@
         <v>480</v>
       </c>
       <c r="C59" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D59" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E59" s="14">
         <v>120</v>
@@ -3674,14 +3674,14 @@
       </c>
       <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>985</v>
       </c>
       <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>455</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L59" s="16" t="s">
         <v>50</v>
@@ -3690,7 +3690,7 @@
         <v>66</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3701,10 +3701,10 @@
         <v>420</v>
       </c>
       <c r="C60" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D60" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E60" s="14">
         <v>90</v>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>540</v>
       </c>
       <c r="K60" s="16" t="s">
         <v>57</v>
@@ -3736,7 +3736,7 @@
         <v>59</v>
       </c>
       <c r="N60" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -3744,10 +3744,10 @@
         <v>46294</v>
       </c>
       <c r="B61" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="C61" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D61" s="14">
         <v>0</v>
@@ -3764,25 +3764,25 @@
       <c r="H61" s="14">
         <v>0</v>
       </c>
-      <c r="I61" s="15" t="str">
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>445</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>995</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M61" s="16" t="s">
         <v>59</v>
       </c>
       <c r="N61" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="58" x14ac:dyDescent="0.35">
@@ -3793,7 +3793,7 @@
         <v>480</v>
       </c>
       <c r="C62" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D62" s="14">
         <v>240</v>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="K62" s="16" t="s">
         <v>57</v>
@@ -3828,7 +3828,7 @@
         <v>59</v>
       </c>
       <c r="N62" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3839,7 +3839,7 @@
         <v>480</v>
       </c>
       <c r="C63" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D63" s="14">
         <v>360</v>
@@ -3858,11 +3858,11 @@
       </c>
       <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>64</v>
@@ -3874,7 +3874,7 @@
         <v>66</v>
       </c>
       <c r="N63" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3885,7 +3885,7 @@
         <v>480</v>
       </c>
       <c r="C64" s="14">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D64" s="14">
         <v>360</v>
@@ -3904,11 +3904,11 @@
       </c>
       <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="K64" s="16" t="s">
         <v>65</v>
@@ -3920,7 +3920,7 @@
         <v>66</v>
       </c>
       <c r="N64" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3931,7 +3931,7 @@
         <v>480</v>
       </c>
       <c r="C65" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D65" s="14">
         <v>360</v>
@@ -3950,11 +3950,11 @@
       </c>
       <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="K65" s="16" t="s">
         <v>49</v>
@@ -3969,27 +3969,51 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+    <row r="66" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B66" s="14">
+        <v>480</v>
+      </c>
+      <c r="C66" s="14">
+        <v>35</v>
+      </c>
+      <c r="D66" s="14">
+        <v>355</v>
+      </c>
+      <c r="E66" s="14">
+        <v>80</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>40</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1664" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36383E26-0831-4920-9FCB-732115ED0BED}"/>
+  <xr:revisionPtr revIDLastSave="1678" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E126F7BF-47B1-4455-91AC-86F1F6D89979}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>A highly productive day with a perfect blend of learning and execution.</t>
   </si>
 </sst>
 </file>
@@ -3923,27 +3926,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+    <row r="66" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B66" s="9">
+        <v>480</v>
+      </c>
+      <c r="C66" s="9">
+        <v>35</v>
+      </c>
+      <c r="D66" s="9">
+        <v>360</v>
+      </c>
+      <c r="E66" s="9">
+        <v>120</v>
+      </c>
+      <c r="F66" s="9">
+        <v>250</v>
+      </c>
+      <c r="G66" s="9">
+        <v>5</v>
+      </c>
+      <c r="H66" s="9">
+        <v>30</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>165</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1678" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E126F7BF-47B1-4455-91AC-86F1F6D89979}"/>
+  <xr:revisionPtr revIDLastSave="1694" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF342C7A-1979-4EC5-8825-27B188A24F7D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>A highly productive day with a perfect blend of learning and execution.</t>
+  </si>
+  <si>
+    <t>Attended online classes and fully focused on midterm preparation</t>
   </si>
 </sst>
 </file>
@@ -3972,27 +3975,51 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+    <row r="67" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B67" s="9">
+        <v>480</v>
+      </c>
+      <c r="C67" s="9">
+        <v>40</v>
+      </c>
+      <c r="D67" s="9">
+        <v>360</v>
+      </c>
+      <c r="E67" s="9">
+        <v>110</v>
+      </c>
+      <c r="F67" s="9">
+        <v>250</v>
+      </c>
+      <c r="G67" s="9">
+        <v>5</v>
+      </c>
+      <c r="H67" s="9">
+        <v>30</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1694" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF342C7A-1979-4EC5-8825-27B188A24F7D}"/>
+  <xr:revisionPtr revIDLastSave="1706" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A9BBB9C-098F-4B4F-A66D-99D29925ED72}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>Attended online classes and fully focused on midterm preparation</t>
+  </si>
+  <si>
+    <t>Attended online classes and fully focused on midterm preparation.</t>
   </si>
 </sst>
 </file>
@@ -4021,27 +4024,51 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+    <row r="68" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B68" s="9">
+        <v>480</v>
+      </c>
+      <c r="C68" s="9">
+        <v>40</v>
+      </c>
+      <c r="D68" s="9">
+        <v>360</v>
+      </c>
+      <c r="E68" s="9">
+        <v>120</v>
+      </c>
+      <c r="F68" s="9">
+        <v>200</v>
+      </c>
+      <c r="G68" s="9">
+        <v>4</v>
+      </c>
+      <c r="H68" s="9">
+        <v>40</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1706" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A9BBB9C-098F-4B4F-A66D-99D29925ED72}"/>
+  <xr:revisionPtr revIDLastSave="1750" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E120C990-B9B5-49C7-98F0-9731FBC22169}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>Attended online classes and fully focused on midterm preparation.</t>
+  </si>
+  <si>
+    <t>A neutral and balanced day focused on completing routine self-study and maintaining standard coding targets.</t>
+  </si>
+  <si>
+    <t>A Satisfying and productive day with consistent study, elevated coding time, and stable energy level.</t>
   </si>
 </sst>
 </file>
@@ -4070,71 +4076,143 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+    <row r="69" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B69" s="9">
+        <v>480</v>
+      </c>
+      <c r="C69" s="9">
+        <v>40</v>
+      </c>
+      <c r="D69" s="9">
+        <v>360</v>
+      </c>
+      <c r="E69" s="9">
+        <v>110</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>45</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+        <v>405</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A70" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B70" s="9">
+        <v>480</v>
+      </c>
+      <c r="C70" s="9">
+        <v>40</v>
+      </c>
+      <c r="D70" s="9">
+        <v>360</v>
+      </c>
+      <c r="E70" s="9">
+        <v>100</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>45</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+        <v>415</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A71" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B71" s="9">
+        <v>480</v>
+      </c>
+      <c r="C71" s="9">
+        <v>40</v>
+      </c>
+      <c r="D71" s="9">
+        <v>360</v>
+      </c>
+      <c r="E71" s="9">
+        <v>110</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>45</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>405</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1750" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E120C990-B9B5-49C7-98F0-9731FBC22169}"/>
+  <xr:revisionPtr revIDLastSave="1786" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AD1FD1-6615-4DC1-96FD-8E6CE104A553}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,15 @@
   </si>
   <si>
     <t>A Satisfying and productive day with consistent study, elevated coding time, and stable energy level.</t>
+  </si>
+  <si>
+    <t>Achieved excellent daily balance with dedicated study time and stable energy levels.</t>
+  </si>
+  <si>
+    <t>Successfully started my mid-term examinations today while maintaining consistent hours for study and wellness.</t>
+  </si>
+  <si>
+    <t>Continued mid-term preparations with a 8 hours of studying and coding, while maintaining stable energy levels.</t>
   </si>
 </sst>
 </file>
@@ -4214,71 +4223,143 @@
         <v>122</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+    <row r="72" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B72" s="9">
+        <v>480</v>
+      </c>
+      <c r="C72" s="9">
+        <v>40</v>
+      </c>
+      <c r="D72" s="9">
+        <v>420</v>
+      </c>
+      <c r="E72" s="9">
+        <v>100</v>
+      </c>
+      <c r="F72" s="9">
+        <v>0</v>
+      </c>
+      <c r="G72" s="9">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9">
+        <v>45</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+        <v>355</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A73" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B73" s="9">
+        <v>480</v>
+      </c>
+      <c r="C73" s="9">
+        <v>40</v>
+      </c>
+      <c r="D73" s="9">
+        <v>480</v>
+      </c>
+      <c r="E73" s="9">
+        <v>100</v>
+      </c>
+      <c r="F73" s="9">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9">
+        <v>45</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+        <v>295</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B74" s="9">
+        <v>480</v>
+      </c>
+      <c r="C74" s="9">
+        <v>40</v>
+      </c>
+      <c r="D74" s="9">
+        <v>480</v>
+      </c>
+      <c r="E74" s="9">
+        <v>100</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>40</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1786" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AD1FD1-6615-4DC1-96FD-8E6CE104A553}"/>
+  <xr:revisionPtr revIDLastSave="1823" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471D5092-73A6-4B6A-B50D-22B65777D546}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -413,6 +413,15 @@
   </si>
   <si>
     <t>Continued mid-term preparations with a 8 hours of studying and coding, while maintaining stable energy levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced mid-term exams with 8 hours of study and coding practice while keeping a medium energy level.  </t>
+  </si>
+  <si>
+    <t>Achieved peak productivity with 9 hours of study and high energy on a non-exam day, feeling completely satisfied.</t>
+  </si>
+  <si>
+    <t>Maintained a steady study and coding routine alongside mid-term exams, keeping energy levels consistent.</t>
   </si>
 </sst>
 </file>
@@ -4361,71 +4370,143 @@
         <v>125</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+    <row r="75" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A75" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B75" s="9">
+        <v>480</v>
+      </c>
+      <c r="C75" s="9">
+        <v>40</v>
+      </c>
+      <c r="D75" s="9">
+        <v>480</v>
+      </c>
+      <c r="E75" s="9">
+        <v>100</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>45</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+        <v>295</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A76" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B76" s="9">
+        <v>480</v>
+      </c>
+      <c r="C76" s="9">
+        <v>40</v>
+      </c>
+      <c r="D76" s="9">
+        <v>540</v>
+      </c>
+      <c r="E76" s="9">
+        <v>100</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>45</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+        <v>235</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A77" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B77" s="9">
+        <v>480</v>
+      </c>
+      <c r="C77" s="9">
+        <v>40</v>
+      </c>
+      <c r="D77" s="9">
+        <v>480</v>
+      </c>
+      <c r="E77" s="9">
+        <v>100</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>45</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1823" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471D5092-73A6-4B6A-B50D-22B65777D546}"/>
+  <xr:revisionPtr revIDLastSave="1850" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{747AC1C7-13D7-44F3-BAE3-710225101F75}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="131">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -422,6 +422,12 @@
   </si>
   <si>
     <t>Maintained a steady study and coding routine alongside mid-term exams, keeping energy levels consistent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieved a peak of 8 hours of study and 100 minutes of coding resulting in a excellent day. </t>
+  </si>
+  <si>
+    <t>Maintained 8 hours of study with maximum energy levels and highly satisfactory performance.</t>
   </si>
 </sst>
 </file>
@@ -4508,49 +4514,97 @@
         <v>128</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+    <row r="78" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A78" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B78" s="9">
+        <v>480</v>
+      </c>
+      <c r="C78" s="9">
+        <v>45</v>
+      </c>
+      <c r="D78" s="9">
+        <v>540</v>
+      </c>
+      <c r="E78" s="9">
+        <v>100</v>
+      </c>
+      <c r="F78" s="9">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>45</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+        <v>230</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A79" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B79" s="9">
+        <v>480</v>
+      </c>
+      <c r="C79" s="9">
+        <v>45</v>
+      </c>
+      <c r="D79" s="9">
+        <v>480</v>
+      </c>
+      <c r="E79" s="9">
+        <v>100</v>
+      </c>
+      <c r="F79" s="9">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9">
+        <v>0</v>
+      </c>
+      <c r="H79" s="9">
+        <v>45</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>290</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1850" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{747AC1C7-13D7-44F3-BAE3-710225101F75}"/>
+  <xr:revisionPtr revIDLastSave="1883" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088DA85D-312E-443C-A797-4B06D15EA041}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -428,6 +428,12 @@
   </si>
   <si>
     <t>Maintained 8 hours of study with maximum energy levels and highly satisfactory performance.</t>
+  </si>
+  <si>
+    <t>A highly efficient day balanced with active learning, 40 minutes of fitness, and an excellent overall feeling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showcased strong academic commitment with extensive study sessions and high energy levels throughout the day. </t>
   </si>
 </sst>
 </file>
@@ -4606,49 +4612,97 @@
         <v>130</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+    <row r="80" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A80" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B80" s="9">
+        <v>420</v>
+      </c>
+      <c r="C80" s="9">
+        <v>40</v>
+      </c>
+      <c r="D80" s="9">
+        <v>180</v>
+      </c>
+      <c r="E80" s="9">
+        <v>190</v>
+      </c>
+      <c r="F80" s="9">
+        <v>250</v>
+      </c>
+      <c r="G80" s="9">
+        <v>5</v>
+      </c>
+      <c r="H80" s="9">
+        <v>45</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+        <v>315</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A81" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B81" s="9">
+        <v>480</v>
+      </c>
+      <c r="C81" s="9">
+        <v>60</v>
+      </c>
+      <c r="D81" s="9">
+        <v>180</v>
+      </c>
+      <c r="E81" s="9">
+        <v>190</v>
+      </c>
+      <c r="F81" s="9">
+        <v>0</v>
+      </c>
+      <c r="G81" s="9">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9">
+        <v>45</v>
+      </c>
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>955</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
+        <v>485</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1883" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088DA85D-312E-443C-A797-4B06D15EA041}"/>
+  <xr:revisionPtr revIDLastSave="1896" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3FD6BEF-16E9-4892-B62A-0DB5E5E0D013}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="134">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t xml:space="preserve">Showcased strong academic commitment with extensive study sessions and high energy levels throughout the day. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstrated excellent academic consistency with high energy balanced across classes, self-study, and daily fitness. </t>
   </si>
 </sst>
 </file>
@@ -4704,27 +4707,51 @@
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
+    <row r="82" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A82" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B82" s="9">
+        <v>480</v>
+      </c>
+      <c r="C82" s="9">
+        <v>60</v>
+      </c>
+      <c r="D82" s="9">
+        <v>180</v>
+      </c>
+      <c r="E82" s="9">
+        <v>120</v>
+      </c>
+      <c r="F82" s="9">
+        <v>200</v>
+      </c>
+      <c r="G82" s="9">
+        <v>4</v>
+      </c>
+      <c r="H82" s="9">
+        <v>45</v>
+      </c>
+      <c r="I82" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J82" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="12"/>
+        <v>355</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1896" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3FD6BEF-16E9-4892-B62A-0DB5E5E0D013}"/>
+  <xr:revisionPtr revIDLastSave="1908" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9D065D-678C-47C1-B210-535BA9879C77}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="135">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -437,6 +437,9 @@
   </si>
   <si>
     <t xml:space="preserve">Demonstrated excellent academic consistency with high energy balanced across classes, self-study, and daily fitness. </t>
+  </si>
+  <si>
+    <t>Maintained a perfect balance between academic commitments, intensive coding , and daily physical well-being.</t>
   </si>
 </sst>
 </file>
@@ -4753,27 +4756,51 @@
         <v>133</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
+    <row r="83" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A83" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B83" s="9">
+        <v>480</v>
+      </c>
+      <c r="C83" s="9">
+        <v>60</v>
+      </c>
+      <c r="D83" s="9">
+        <v>180</v>
+      </c>
+      <c r="E83" s="9">
+        <v>180</v>
+      </c>
+      <c r="F83" s="9">
+        <v>300</v>
+      </c>
+      <c r="G83" s="9">
+        <v>6</v>
+      </c>
+      <c r="H83" s="9">
+        <v>45</v>
+      </c>
+      <c r="I83" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J83" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="12"/>
+        <v>195</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1908" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9D065D-678C-47C1-B210-535BA9879C77}"/>
+  <xr:revisionPtr revIDLastSave="1921" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FB7516-6177-454A-B500-4AFB5D69255C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="136">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>Maintained a perfect balance between academic commitments, intensive coding , and daily physical well-being.</t>
+  </si>
+  <si>
+    <t>A highly productive, balanced, and energetic day with excellent progress in both studies and health.</t>
   </si>
 </sst>
 </file>
@@ -4802,27 +4805,51 @@
         <v>134</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10" t="str">
+    <row r="84" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A84" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B84" s="9">
+        <v>480</v>
+      </c>
+      <c r="C84" s="9">
+        <v>60</v>
+      </c>
+      <c r="D84" s="9">
+        <v>180</v>
+      </c>
+      <c r="E84" s="9">
+        <v>180</v>
+      </c>
+      <c r="F84" s="9">
+        <v>250</v>
+      </c>
+      <c r="G84" s="9">
+        <v>5</v>
+      </c>
+      <c r="H84" s="9">
+        <v>60</v>
+      </c>
+      <c r="I84" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J84" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N84" s="12" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1921" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FB7516-6177-454A-B500-4AFB5D69255C}"/>
+  <xr:revisionPtr revIDLastSave="1935" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4488335-6FDA-4FD9-9713-F7A89B41C679}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="137">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>A highly productive, balanced, and energetic day with excellent progress in both studies and health.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Achieved peak productivity by perfectly balancing 6 hours of studies and coding with an active fitness routine and optimal rest.</t>
   </si>
 </sst>
 </file>
@@ -4851,27 +4854,51 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="10" t="str">
+    <row r="85" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B85" s="9">
+        <v>480</v>
+      </c>
+      <c r="C85" s="9">
+        <v>60</v>
+      </c>
+      <c r="D85" s="9">
+        <v>180</v>
+      </c>
+      <c r="E85" s="9">
+        <v>180</v>
+      </c>
+      <c r="F85" s="9">
+        <v>100</v>
+      </c>
+      <c r="G85" s="9">
+        <v>1</v>
+      </c>
+      <c r="H85" s="9">
+        <v>60</v>
+      </c>
+      <c r="I85" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J85" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N85" s="12" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roshani Kumari\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1935" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4488335-6FDA-4FD9-9713-F7A89B41C679}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="140">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t xml:space="preserve"> Achieved peak productivity by perfectly balancing 6 hours of studies and coding with an active fitness routine and optimal rest.</t>
+  </si>
+  <si>
+    <t>Utilized the day off from classes effectively to maximize self-study while ensuring sufficient personal time to recharge.</t>
+  </si>
+  <si>
+    <t>Productive day off with 7 hours of study and coding, balanced with personal time.</t>
+  </si>
+  <si>
+    <t>Maintained consistency in productivity with a high energy level and balanced study hours.</t>
   </si>
 </sst>
 </file>
@@ -718,10 +727,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4900,71 +4905,143 @@
         <v>136</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="10" t="str">
+    <row r="86" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A86" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B86" s="9">
+        <v>480</v>
+      </c>
+      <c r="C86" s="9">
+        <v>60</v>
+      </c>
+      <c r="D86" s="9">
+        <v>240</v>
+      </c>
+      <c r="E86" s="9">
+        <v>180</v>
+      </c>
+      <c r="F86" s="9">
+        <v>0</v>
+      </c>
+      <c r="G86" s="9">
+        <v>0</v>
+      </c>
+      <c r="H86" s="9">
+        <v>60</v>
+      </c>
+      <c r="I86" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J86" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="12"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="10" t="str">
+        <v>420</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M86" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N86" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B87" s="9">
+        <v>480</v>
+      </c>
+      <c r="C87" s="9">
+        <v>60</v>
+      </c>
+      <c r="D87" s="9">
+        <v>240</v>
+      </c>
+      <c r="E87" s="9">
+        <v>180</v>
+      </c>
+      <c r="F87" s="9">
+        <v>0</v>
+      </c>
+      <c r="G87" s="9">
+        <v>0</v>
+      </c>
+      <c r="H87" s="9">
+        <v>60</v>
+      </c>
+      <c r="I87" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J87" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="12"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="10" t="str">
+        <v>420</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N87" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B88" s="9">
+        <v>480</v>
+      </c>
+      <c r="C88" s="9">
+        <v>60</v>
+      </c>
+      <c r="D88" s="9">
+        <v>240</v>
+      </c>
+      <c r="E88" s="9">
+        <v>180</v>
+      </c>
+      <c r="F88" s="9">
+        <v>250</v>
+      </c>
+      <c r="G88" s="9">
+        <v>5</v>
+      </c>
+      <c r="H88" s="9">
+        <v>60</v>
+      </c>
+      <c r="I88" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="10" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J88" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="11"/>
-      <c r="N88" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M88" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N88" s="12" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roshani Kumari\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D7649A-CCE9-41E1-B01E-AA6E8F9AA991}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="141">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>Maintained consistency in productivity with a high energy level and balanced study hours.</t>
+  </si>
+  <si>
+    <t>Successfully balanced classes and personal study goals while maintaining high energy levels.</t>
   </si>
 </sst>
 </file>
@@ -5043,27 +5046,51 @@
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="10" t="str">
+    <row r="89" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B89" s="9">
+        <v>480</v>
+      </c>
+      <c r="C89" s="9">
+        <v>60</v>
+      </c>
+      <c r="D89" s="9">
+        <v>240</v>
+      </c>
+      <c r="E89" s="9">
+        <v>180</v>
+      </c>
+      <c r="F89" s="9">
+        <v>200</v>
+      </c>
+      <c r="G89" s="9">
+        <v>4</v>
+      </c>
+      <c r="H89" s="9">
+        <v>60</v>
+      </c>
+      <c r="I89" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J89" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J89" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-      <c r="M89" s="11"/>
-      <c r="N89" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M89" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N89" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D7649A-CCE9-41E1-B01E-AA6E8F9AA991}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D23D39D-0ECC-4ED7-A46E-F61169323906}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="142">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>Successfully balanced classes and personal study goals while maintaining high energy levels.</t>
+  </si>
+  <si>
+    <t>High energy levels and satisfied day with 7 hours of study and coding, balanced with personal time.</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5092,27 +5099,51 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="10" t="str">
+    <row r="90" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A90" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B90" s="9">
+        <v>480</v>
+      </c>
+      <c r="C90" s="9">
+        <v>60</v>
+      </c>
+      <c r="D90" s="9">
+        <v>260</v>
+      </c>
+      <c r="E90" s="9">
+        <v>170</v>
+      </c>
+      <c r="F90" s="9">
+        <v>300</v>
+      </c>
+      <c r="G90" s="9">
+        <v>6</v>
+      </c>
+      <c r="H90" s="9">
+        <v>60</v>
+      </c>
+      <c r="I90" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J90" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J90" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
-      <c r="M90" s="11"/>
-      <c r="N90" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L90" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M90" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N90" s="12" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D23D39D-0ECC-4ED7-A46E-F61169323906}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D44CE6B-8FAD-4304-8C66-DB921FC00F23}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="143">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>High energy levels and satisfied day with 7 hours of study and coding, balanced with personal time.</t>
+  </si>
+  <si>
+    <t>Maintained excellent productivity with 7 hours of study, coding and 7 classes attended.</t>
   </si>
 </sst>
 </file>
@@ -5145,27 +5148,51 @@
         <v>141</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="10" t="str">
+    <row r="91" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A91" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B91" s="9">
+        <v>480</v>
+      </c>
+      <c r="C91" s="9">
+        <v>60</v>
+      </c>
+      <c r="D91" s="9">
+        <v>240</v>
+      </c>
+      <c r="E91" s="9">
+        <v>180</v>
+      </c>
+      <c r="F91" s="9">
+        <v>350</v>
+      </c>
+      <c r="G91" s="9">
+        <v>7</v>
+      </c>
+      <c r="H91" s="9">
+        <v>60</v>
+      </c>
+      <c r="I91" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J91" s="10" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J91" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
-      <c r="M91" s="11"/>
-      <c r="N91" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L91" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M91" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N91" s="12" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D44CE6B-8FAD-4304-8C66-DB921FC00F23}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB1E444-A75B-45AD-9B73-6EC9B3E2CC08}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -464,6 +464,9 @@
   </si>
   <si>
     <t>Maintained excellent productivity with 7 hours of study, coding and 7 classes attended.</t>
+  </si>
+  <si>
+    <t>Maintained high energy levels and personal goals with balanced personal time.</t>
   </si>
 </sst>
 </file>
@@ -5194,27 +5197,51 @@
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="10" t="str">
+    <row r="92" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="8">
+        <v>46326</v>
+      </c>
+      <c r="B92" s="9">
+        <v>480</v>
+      </c>
+      <c r="C92" s="9">
+        <v>60</v>
+      </c>
+      <c r="D92" s="9">
+        <v>240</v>
+      </c>
+      <c r="E92" s="9">
+        <v>180</v>
+      </c>
+      <c r="F92" s="9">
+        <v>200</v>
+      </c>
+      <c r="G92" s="9">
+        <v>4</v>
+      </c>
+      <c r="H92" s="9">
+        <v>60</v>
+      </c>
+      <c r="I92" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J92" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J92" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K92" s="11"/>
-      <c r="L92" s="11"/>
-      <c r="M92" s="11"/>
-      <c r="N92" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M92" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N92" s="12" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="8"/>

--- a/12600317.xlsx
+++ b/12600317.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80c588e9b1244fd9/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB1E444-A75B-45AD-9B73-6EC9B3E2CC08}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{18A1319B-4C07-4995-9FBD-0EB302FA1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D58098E-F5FC-4DA5-B23A-7DC5B8B4CC9A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="145">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -467,6 +467,9 @@
   </si>
   <si>
     <t>Maintained high energy levels and personal goals with balanced personal time.</t>
+  </si>
+  <si>
+    <t>Maintained high energy levels and personal goals with balanced personal time on a class-free day.</t>
   </si>
 </sst>
 </file>
@@ -5243,27 +5246,51 @@
         <v>143</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="10" t="str">
+    <row r="93" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A93" s="8">
+        <v>46327</v>
+      </c>
+      <c r="B93" s="9">
+        <v>480</v>
+      </c>
+      <c r="C93" s="9">
+        <v>60</v>
+      </c>
+      <c r="D93" s="9">
+        <v>260</v>
+      </c>
+      <c r="E93" s="9">
+        <v>190</v>
+      </c>
+      <c r="F93" s="9">
+        <v>0</v>
+      </c>
+      <c r="G93" s="9">
+        <v>0</v>
+      </c>
+      <c r="H93" s="9">
+        <v>60</v>
+      </c>
+      <c r="I93" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J93" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J93" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M93" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N93" s="12" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="8"/>
